--- a/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>SMMT</t>
   </si>
@@ -656,53 +656,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43496</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43131</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -712,33 +712,36 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>57100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -748,9 +751,12 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -784,9 +790,12 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,9 +829,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,32 +849,33 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>580400</v>
+      </c>
+      <c r="E12" s="3">
         <v>51100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>84300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>38800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>50900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>37600</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,33 +924,36 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>8500</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>5300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -944,33 +963,36 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
@@ -980,9 +1002,12 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,32 +1019,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>609700</v>
+      </c>
+      <c r="E17" s="3">
         <v>72800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>88000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>54100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>51100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44500</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,33 +1055,36 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-72100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-86200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-53200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-27500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28400</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,9 +1094,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,32 +1114,33 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,33 +1150,36 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-598300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-73100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-87000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-51100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25500</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,17 +1189,20 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E22" s="3">
         <v>4400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
@@ -1171,8 +1210,8 @@
       <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>300</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1186,36 +1225,39 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-78800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-88600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-52900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25900</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,33 +1267,36 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,9 +1306,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,33 +1345,36 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-78800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-88600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-52700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26400</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,33 +1384,36 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-78800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-88600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-52700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26400</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1369,9 +1423,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,33 +1579,36 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,33 +1618,36 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-78800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-88600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-52700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26400</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,9 +1657,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,33 +1696,36 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-78800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-88600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-52700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26400</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,38 +1735,41 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43496</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43131</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1698,9 +1779,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,32 +1816,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E41" s="3">
         <v>348600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>63800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1766,32 +1852,35 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>114800</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1802,33 +1891,36 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1838,9 +1930,12 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1874,33 +1969,36 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E45" s="3">
         <v>302000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1910,33 +2008,36 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>189700</v>
+      </c>
+      <c r="E46" s="3">
         <v>656700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>97300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>79600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1946,32 +2047,35 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1982,33 +2086,36 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,33 +2125,36 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24500</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2054,9 +2164,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,21 +2242,24 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2156,15 +2275,18 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,33 +2320,36 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>202900</v>
+      </c>
+      <c r="E54" s="3">
         <v>664200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>113400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>102500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>79600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,9 +2359,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,32 +2396,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,18 +2432,21 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>19800</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,8 +2462,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2338,33 +2471,36 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E59" s="3">
         <v>18700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2374,33 +2510,36 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E60" s="3">
         <v>38800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,18 +2549,21 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E61" s="3">
         <v>494500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -2432,11 +2574,11 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>4400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2446,33 +2588,36 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E62" s="3">
         <v>4200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>45700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2482,9 +2627,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,33 +2744,36 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E66" s="3">
         <v>537500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82700</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2626,9 +2783,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2878,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,33 +2956,36 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-993300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-378300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-299500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-210900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-158200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-130900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-140800</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2822,9 +2995,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,33 +3112,36 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E76" s="3">
         <v>126700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>83300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>78900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>55800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,9 +3151,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,38 +3190,41 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43496</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43131</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3043,33 +3234,36 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-78800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-88600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-52700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26400</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,9 +3273,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,32 +3293,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>1300</v>
       </c>
       <c r="F83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,9 +3329,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,33 +3524,36 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-76800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-41600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-72600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-48100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21500</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,9 +3563,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,32 +3583,33 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3399,9 +3619,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,33 +3697,36 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-587800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-300</v>
       </c>
       <c r="H94" s="3">
         <v>-300</v>
       </c>
       <c r="I94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-7000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,9 +3736,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3559,9 +3792,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,33 +3909,36 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E100" s="3">
         <v>620200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>77900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>50600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>49500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>44500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18800</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3703,33 +3948,36 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2900</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,33 +3987,36 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-577200</v>
+      </c>
+      <c r="E102" s="3">
         <v>576800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6800</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3775,7 +4026,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>SMMT</t>
   </si>
@@ -734,13 +734,13 @@
         <v>900</v>
       </c>
       <c r="H8" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I8" s="3">
         <v>57100</v>
       </c>
       <c r="J8" s="3">
-        <v>16100</v>
+        <v>20100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -802,23 +802,23 @@
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>57100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>20100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -856,25 +856,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>580400</v>
+        <v>59500</v>
       </c>
       <c r="E12" s="3">
-        <v>51100</v>
+        <v>53300</v>
       </c>
       <c r="F12" s="3">
-        <v>84300</v>
+        <v>85400</v>
       </c>
       <c r="G12" s="3">
+        <v>53300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>43400</v>
+      </c>
+      <c r="I12" s="3">
         <v>52000</v>
       </c>
-      <c r="H12" s="3">
-        <v>38800</v>
-      </c>
-      <c r="I12" s="3">
-        <v>50900</v>
-      </c>
       <c r="J12" s="3">
-        <v>37600</v>
+        <v>41200</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -934,25 +934,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>520900</v>
       </c>
       <c r="E14" s="3">
-        <v>8500</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>7200</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
-        <v>5300</v>
+        <v>4600</v>
       </c>
       <c r="J14" s="3">
-        <v>500</v>
+        <v>-5700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -973,25 +973,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="F15" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="G15" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="H15" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1026,25 +1026,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>609700</v>
+        <v>88700</v>
       </c>
       <c r="E17" s="3">
-        <v>72800</v>
+        <v>65600</v>
       </c>
       <c r="F17" s="3">
         <v>88000</v>
       </c>
       <c r="G17" s="3">
-        <v>54100</v>
+        <v>53200</v>
       </c>
       <c r="H17" s="3">
-        <v>28200</v>
+        <v>30800</v>
       </c>
       <c r="I17" s="3">
-        <v>51100</v>
+        <v>47100</v>
       </c>
       <c r="J17" s="3">
-        <v>44500</v>
+        <v>58100</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1064,26 +1064,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-88700</v>
       </c>
       <c r="E18" s="3">
-        <v>-72100</v>
+        <v>-64900</v>
       </c>
       <c r="F18" s="3">
         <v>-86200</v>
       </c>
       <c r="G18" s="3">
-        <v>-53200</v>
+        <v>-52300</v>
       </c>
       <c r="H18" s="3">
         <v>-27500</v>
       </c>
       <c r="I18" s="3">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="J18" s="3">
-        <v>-28400</v>
+        <v>-38000</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1120,26 +1120,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-800</v>
       </c>
       <c r="E20" s="3">
-        <v>-2300</v>
+        <v>3800</v>
       </c>
       <c r="F20" s="3">
-        <v>-2100</v>
+        <v>2200</v>
       </c>
       <c r="G20" s="3">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="H20" s="3">
-        <v>-1300</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="3">
-        <v>3100</v>
+        <v>-4300</v>
       </c>
       <c r="J20" s="3">
-        <v>2500</v>
+        <v>1700</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1160,25 +1160,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-598300</v>
+        <v>-87800</v>
       </c>
       <c r="E21" s="3">
-        <v>-73100</v>
+        <v>-67400</v>
       </c>
       <c r="F21" s="3">
         <v>-87000</v>
       </c>
       <c r="G21" s="3">
-        <v>-51100</v>
+        <v>-50200</v>
       </c>
       <c r="H21" s="3">
-        <v>-27500</v>
+        <v>-27400</v>
       </c>
       <c r="I21" s="3">
-        <v>10800</v>
+        <v>15800</v>
       </c>
       <c r="J21" s="3">
-        <v>-25500</v>
+        <v>-39100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1205,7 +1205,7 @@
         <v>4400</v>
       </c>
       <c r="F22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
@@ -1213,11 +1213,11 @@
       <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>9100</v>
       </c>
       <c r="J23" s="3">
-        <v>-25900</v>
+        <v>-34000</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1282,8 +1282,8 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>-200</v>
@@ -1292,10 +1292,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>-800</v>
+        <v>-1800</v>
       </c>
       <c r="J24" s="3">
-        <v>500</v>
+        <v>-5300</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1370,10 +1370,10 @@
         <v>-29100</v>
       </c>
       <c r="I26" s="3">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="J26" s="3">
-        <v>-26400</v>
+        <v>-28600</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1409,10 +1409,10 @@
         <v>-29100</v>
       </c>
       <c r="I27" s="3">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="J27" s="3">
-        <v>-26400</v>
+        <v>-28600</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1588,26 +1588,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>800</v>
       </c>
       <c r="E32" s="3">
-        <v>2300</v>
+        <v>-3800</v>
       </c>
       <c r="F32" s="3">
-        <v>2100</v>
+        <v>-2200</v>
       </c>
       <c r="G32" s="3">
-        <v>-500</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3">
-        <v>1300</v>
+        <v>-1300</v>
       </c>
       <c r="I32" s="3">
-        <v>-3100</v>
+        <v>4300</v>
       </c>
       <c r="J32" s="3">
-        <v>-2500</v>
+        <v>-1700</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1643,10 +1643,10 @@
         <v>-29100</v>
       </c>
       <c r="I33" s="3">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="J33" s="3">
-        <v>-26400</v>
+        <v>-28600</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1721,10 +1721,10 @@
         <v>-29100</v>
       </c>
       <c r="I35" s="3">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="J35" s="3">
-        <v>-26400</v>
+        <v>-28600</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1838,10 +1838,10 @@
         <v>63800</v>
       </c>
       <c r="I41" s="3">
-        <v>35200</v>
+        <v>35300</v>
       </c>
       <c r="J41" s="3">
-        <v>28500</v>
+        <v>28600</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1864,23 +1864,23 @@
       <c r="D42" s="3">
         <v>114800</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>5600</v>
       </c>
       <c r="I43" s="3">
-        <v>14400</v>
+        <v>16300</v>
       </c>
       <c r="J43" s="3">
-        <v>10500</v>
+        <v>22400</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1939,26 +1939,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1979,25 +1979,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2600</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>302000</v>
+        <v>500</v>
       </c>
       <c r="F45" s="3">
-        <v>8400</v>
+        <v>1200</v>
       </c>
       <c r="G45" s="3">
-        <v>11100</v>
+        <v>1500</v>
       </c>
       <c r="H45" s="3">
-        <v>10200</v>
+        <v>1400</v>
       </c>
       <c r="I45" s="3">
-        <v>11600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>11800</v>
+        <v>8900</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2036,7 +2036,7 @@
         <v>61300</v>
       </c>
       <c r="J46" s="3">
-        <v>50800</v>
+        <v>50900</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2056,8 +2056,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1000</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -2147,7 +2147,7 @@
         <v>13500</v>
       </c>
       <c r="H49" s="3">
-        <v>10700</v>
+        <v>15100</v>
       </c>
       <c r="I49" s="3">
         <v>16300</v>
@@ -2252,7 +2252,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4300</v>
+        <v>5300</v>
       </c>
       <c r="E52" s="3">
         <v>600</v>
@@ -2345,10 +2345,10 @@
         <v>96200</v>
       </c>
       <c r="I54" s="3">
-        <v>79600</v>
+        <v>79700</v>
       </c>
       <c r="J54" s="3">
-        <v>78200</v>
+        <v>78400</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2421,7 +2421,7 @@
         <v>5800</v>
       </c>
       <c r="J57" s="3">
-        <v>6300</v>
+        <v>12500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2442,25 +2442,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
-        <v>19800</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>21500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>500</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2481,25 +2481,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17700</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>18700</v>
+        <v>700</v>
       </c>
       <c r="F59" s="3">
-        <v>21200</v>
+        <v>8800</v>
       </c>
       <c r="G59" s="3">
-        <v>13800</v>
+        <v>9100</v>
       </c>
       <c r="H59" s="3">
-        <v>9300</v>
+        <v>3100</v>
       </c>
       <c r="I59" s="3">
-        <v>11400</v>
+        <v>5700</v>
       </c>
       <c r="J59" s="3">
-        <v>26300</v>
+        <v>19600</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2559,25 +2559,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100000</v>
+        <v>103300</v>
       </c>
       <c r="E61" s="3">
-        <v>494500</v>
+        <v>497300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J61" s="3">
-        <v>4400</v>
+        <v>1400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2598,25 +2598,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4900</v>
+        <v>1600</v>
       </c>
       <c r="E62" s="3">
-        <v>4200</v>
+        <v>1400</v>
       </c>
       <c r="F62" s="3">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="G62" s="3">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="H62" s="3">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="I62" s="3">
-        <v>6600</v>
+        <v>2400</v>
       </c>
       <c r="J62" s="3">
-        <v>45700</v>
+        <v>6700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2772,7 +2772,7 @@
         <v>23800</v>
       </c>
       <c r="J66" s="3">
-        <v>82700</v>
+        <v>82800</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2981,10 +2981,10 @@
         <v>-158200</v>
       </c>
       <c r="I72" s="3">
-        <v>-130900</v>
+        <v>-100000</v>
       </c>
       <c r="J72" s="3">
-        <v>-140800</v>
+        <v>-133400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3137,7 +3137,7 @@
         <v>78900</v>
       </c>
       <c r="I76" s="3">
-        <v>55800</v>
+        <v>55900</v>
       </c>
       <c r="J76" s="3">
         <v>-4500</v>
@@ -3259,10 +3259,10 @@
         <v>-29100</v>
       </c>
       <c r="I81" s="3">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="J81" s="3">
-        <v>-26400</v>
+        <v>-28600</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3300,25 +3300,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="E83" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="F83" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="J83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3552,7 +3552,7 @@
         <v>-35100</v>
       </c>
       <c r="J89" s="3">
-        <v>-21500</v>
+        <v>-20700</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3608,7 +3608,7 @@
         <v>-200</v>
       </c>
       <c r="J91" s="3">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3725,7 +3725,7 @@
         <v>-300</v>
       </c>
       <c r="J94" s="3">
-        <v>-7000</v>
+        <v>-7400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3931,13 +3931,13 @@
         <v>50600</v>
       </c>
       <c r="H100" s="3">
-        <v>49500</v>
+        <v>54000</v>
       </c>
       <c r="I100" s="3">
         <v>44500</v>
       </c>
       <c r="J100" s="3">
-        <v>18800</v>
+        <v>19500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3976,7 +3976,7 @@
         <v>-2300</v>
       </c>
       <c r="J101" s="3">
-        <v>2900</v>
+        <v>-2700</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4009,13 +4009,13 @@
         <v>2600</v>
       </c>
       <c r="H102" s="3">
-        <v>28600</v>
+        <v>33100</v>
       </c>
       <c r="I102" s="3">
         <v>6800</v>
       </c>
       <c r="J102" s="3">
-        <v>-6800</v>
+        <v>-11300</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>SMMT</t>
   </si>
@@ -656,56 +656,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43496</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43131</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,36 +715,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>57100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -754,9 +757,12 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -793,36 +799,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>57100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,9 +841,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,35 +862,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>150800</v>
+      </c>
+      <c r="E12" s="3">
         <v>59500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>52000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>85400</v>
+      </c>
+      <c r="H12" s="3">
         <v>53300</v>
       </c>
-      <c r="F12" s="3">
-        <v>85400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>53300</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>43400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>52000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>41200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,9 +901,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,36 +943,39 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E14" s="3">
         <v>520900</v>
       </c>
-      <c r="E14" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>8500</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>4600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -966,36 +985,39 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1300</v>
       </c>
       <c r="F15" s="3">
         <v>1300</v>
       </c>
       <c r="G15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H15" s="3">
         <v>1600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1005,9 +1027,12 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,35 +1045,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E17" s="3">
         <v>88700</v>
       </c>
-      <c r="E17" s="3">
-        <v>65600</v>
-      </c>
       <c r="F17" s="3">
+        <v>64300</v>
+      </c>
+      <c r="G17" s="3">
         <v>88000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1058,36 +1084,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-211000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-88700</v>
       </c>
-      <c r="E18" s="3">
-        <v>-64900</v>
-      </c>
       <c r="F18" s="3">
+        <v>-63600</v>
+      </c>
+      <c r="G18" s="3">
         <v>-86200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-52300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1097,9 +1126,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,35 +1147,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,36 +1186,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-211000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-87800</v>
       </c>
-      <c r="E21" s="3">
-        <v>-67400</v>
-      </c>
       <c r="F21" s="3">
+        <v>-66200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-87000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-50200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-27400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-39100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,35 +1228,38 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E22" s="3">
         <v>16500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>300</v>
       </c>
       <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1228,39 +1267,42 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-614900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-78800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-88600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-52900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34000</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,9 +1312,12 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1285,21 +1330,21 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,9 +1354,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,36 +1396,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-614900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-78800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-88600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-52700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1387,36 +1438,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-614900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-78800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-88600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-52700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,9 +1480,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,9 +1522,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1504,9 +1564,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,36 +1648,39 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,36 +1690,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-614900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-78800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-88600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-52700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,9 +1732,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,36 +1774,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-614900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-78800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-88600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-52700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,41 +1816,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43496</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43131</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1782,9 +1863,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,35 +1902,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E41" s="3">
         <v>71400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>348600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>63800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,18 +1941,21 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>307500</v>
+      </c>
+      <c r="E42" s="3">
         <v>114800</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1894,36 +1983,39 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1933,9 +2025,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1960,8 +2055,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1972,33 +2067,36 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2011,36 +2109,39 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>423800</v>
+      </c>
+      <c r="E46" s="3">
         <v>189700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>656700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>97300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>87700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>79600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>61300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,9 +2151,12 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2077,8 +2181,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2089,36 +2193,39 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E48" s="3">
         <v>6100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2128,9 +2235,12 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2138,26 +2248,26 @@
         <v>1900</v>
       </c>
       <c r="E49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24500</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,9 +2277,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,24 +2361,27 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E52" s="3">
         <v>5300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,15 +2397,18 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,36 +2445,39 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>435600</v>
+      </c>
+      <c r="E54" s="3">
         <v>202900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>664200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>113400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>102500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>96200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>79700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,9 +2487,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,35 +2526,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,26 +2565,29 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>500</v>
       </c>
       <c r="I58" s="3">
         <v>500</v>
@@ -2462,11 +2595,11 @@
       <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3">
+        <v>500</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2474,36 +2607,39 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>700</v>
+      </c>
+      <c r="G59" s="3">
         <v>8800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,36 +2649,39 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E60" s="3">
         <v>20400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2552,36 +2691,39 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E61" s="3">
         <v>103300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>497300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2591,9 +2733,12 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2601,26 +2746,26 @@
         <v>1600</v>
       </c>
       <c r="E62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2630,9 +2775,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,36 +2901,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E66" s="3">
         <v>125300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>537500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2786,9 +2943,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,9 +3045,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,36 +3129,39 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1214600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-993300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-378300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-299500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-210900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-158200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-100000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-133400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,9 +3171,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,36 +3297,39 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>388700</v>
+      </c>
+      <c r="E76" s="3">
         <v>77700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>126700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>83300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>79500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>78900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>55900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-4500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,9 +3339,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,41 +3381,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43496</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43131</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3237,36 +3428,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-614900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-78800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-88600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-52700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,9 +3470,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,35 +3491,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
         <v>1400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3332,9 +3530,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,36 +3740,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-142100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-76800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-72600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-48100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-35100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3566,9 +3782,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,8 +3803,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3593,26 +3813,26 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,9 +3842,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,36 +3926,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-205300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-587800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-300</v>
       </c>
       <c r="I94" s="3">
         <v>-300</v>
       </c>
       <c r="J94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-7400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,9 +3968,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,8 +3989,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3795,9 +4028,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,36 +4154,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>381200</v>
+      </c>
+      <c r="E100" s="3">
         <v>86500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>620200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>77900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>50600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>54000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>44500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>19500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,36 +4196,39 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3990,36 +4238,39 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-577200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>576800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11300</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4029,7 +4280,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>SMMT</t>
   </si>
@@ -656,59 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43496</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43131</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,9 +718,12 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -730,27 +733,27 @@
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -760,9 +763,12 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -802,9 +808,12 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -814,27 +823,27 @@
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>57100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,38 +875,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>537700</v>
+      </c>
+      <c r="E12" s="3">
         <v>150800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>59500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>85400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>53300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>43400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>52000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>41200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,39 +962,42 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>15000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>520900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,9 +1007,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -998,29 +1020,29 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1300</v>
       </c>
       <c r="G15" s="3">
         <v>1300</v>
       </c>
       <c r="H15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,9 +1052,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,38 +1071,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1094400</v>
+      </c>
+      <c r="E17" s="3">
         <v>211000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>88700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>88000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,39 +1113,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1094400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-211000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-88700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-63600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-86200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-52300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-38000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1129,9 +1158,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,38 +1180,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,39 +1222,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1094900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-211000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-87800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-66200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-87000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-50200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-27400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-39100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,38 +1267,41 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>8700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
       </c>
       <c r="J22" s="3">
+        <v>300</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1270,42 +1309,45 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-221300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-614900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-78800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-88600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-52900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-29100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,9 +1357,12 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1333,21 +1378,21 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1357,9 +1402,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,39 +1447,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-221300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-614900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-78800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-88600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-52700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,39 +1492,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-221300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-614900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-78800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-88600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-52700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28600</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,9 +1537,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,39 +1717,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1693,39 +1762,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-221300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-614900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-78800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-88600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-52700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,9 +1807,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,39 +1852,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-221300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-614900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-78800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-88600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-52700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,44 +1897,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43496</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43131</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1866,9 +1947,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,38 +1988,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>225300</v>
+      </c>
+      <c r="E41" s="3">
         <v>104900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>348600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>63800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,21 +2030,24 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>488200</v>
+      </c>
+      <c r="E42" s="3">
         <v>307500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>114800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1986,39 +2075,42 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>600</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,9 +2120,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2058,8 +2153,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2070,9 +2165,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2082,24 +2180,24 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2112,39 +2210,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>720300</v>
+      </c>
+      <c r="E46" s="3">
         <v>423800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>189700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>656700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>87700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>79600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>61300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2154,9 +2255,12 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2184,8 +2288,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2196,39 +2300,42 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E48" s="3">
         <v>7400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2238,39 +2345,42 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E49" s="3">
         <v>1900</v>
       </c>
       <c r="F49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G49" s="3">
         <v>1800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,27 +2480,30 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,15 +2519,18 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,39 +2570,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>751200</v>
+      </c>
+      <c r="E54" s="3">
         <v>435600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>202900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>664200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>113400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>102500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>96200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,9 +2615,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,38 +2656,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2568,29 +2698,32 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
       </c>
       <c r="J58" s="3">
         <v>500</v>
@@ -2598,11 +2731,11 @@
       <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="L58" s="3">
+        <v>500</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2610,39 +2743,42 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>700</v>
       </c>
       <c r="F59" s="3">
         <v>700</v>
       </c>
       <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>8800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2652,39 +2788,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E60" s="3">
         <v>41700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,39 +2833,42 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>103300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>497300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2736,39 +2878,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E62" s="3">
         <v>1600</v>
       </c>
       <c r="F62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,39 +3058,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E66" s="3">
         <v>46800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>125300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>537500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2946,9 +3103,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,39 +3302,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2294200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1214600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-993300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-378300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-299500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-210900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-158200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-100000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-133400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,9 +3347,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,39 +3482,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>658900</v>
+      </c>
+      <c r="E76" s="3">
         <v>388700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>77700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>126700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>83300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>79500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>78900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>55900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-4500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3342,9 +3527,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,44 +3572,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43496</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43131</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3431,39 +3622,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-221300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-614900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-78800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-88600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-52700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,9 +3667,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,8 +3689,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3501,29 +3699,29 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,9 +3731,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,39 +3956,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-322900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-142100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-76800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-72600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-48100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3785,9 +4001,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,38 +4023,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,9 +4065,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,39 +4155,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-205300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-587800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-300</v>
       </c>
       <c r="J94" s="3">
         <v>-300</v>
       </c>
       <c r="K94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L94" s="3">
         <v>-7400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3971,9 +4200,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,39 +4399,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>617500</v>
+      </c>
+      <c r="E100" s="3">
         <v>381200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>86500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>620200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>77900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>50600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>54000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>44500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>19500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,39 +4444,42 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4241,39 +4489,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E102" s="3">
         <v>33800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-577200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>576800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>33100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,7 +4534,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
